--- a/artfynd/A 49232-2025 artfynd.xlsx
+++ b/artfynd/A 49232-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104593903</v>
       </c>
       <c r="B2" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625481.7842356074</v>
+        <v>625482</v>
       </c>
       <c r="R2" t="n">
-        <v>6934475.217570444</v>
+        <v>6934475</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -791,12 +786,7 @@
         <v>106154235</v>
       </c>
       <c r="B3" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625525.0424495243</v>
+        <v>625525</v>
       </c>
       <c r="R3" t="n">
-        <v>6934481.936240934</v>
+        <v>6934482</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -864,19 +854,9 @@
           <t>2021-04-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -912,16 +892,11 @@
         <v>115583810</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -959,7 +934,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skeppsholmen, Midlanda (Skeppsholmen, Midlanda), Mpd</t>
+          <t>Skeppsholmen, Midlanda, Skeppsholmen, Midlanda, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1035,37 +1010,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118006306</v>
+        <v>124266091</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>100110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1073,21 +1043,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skeppsholmen, Midlanda (Skeppsholmen, Midlanda), Mpd</t>
+          <t>Såggrundet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625505</v>
+        <v>625522</v>
       </c>
       <c r="R5" t="n">
-        <v>6934546</v>
+        <v>6934522</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,12 +1087,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,44 +1117,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Edman</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Edman, Stefan Heimdahl</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124266091</v>
+        <v>118006306</v>
       </c>
       <c r="B6" t="n">
-        <v>57676</v>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100110</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1179,24 +1162,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Såggrundet, Mpd</t>
+          <t>Skeppsholmen, Midlanda, Skeppsholmen, Midlanda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625522</v>
+        <v>625505</v>
       </c>
       <c r="R6" t="n">
-        <v>6934522</v>
+        <v>6934546</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,22 +1203,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,12 +1223,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Granfeldt</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Granfeldt</t>
+          <t>Mattias Edman, Stefan Heimdahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
